--- a/data/pitch_data.xlsx
+++ b/data/pitch_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4403" uniqueCount="805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4616" uniqueCount="806">
   <si>
     <t>PitchNo</t>
   </si>
@@ -2420,6 +2420,9 @@
   </si>
   <si>
     <t>#17 加藤 泰靖</t>
+  </si>
+  <si>
+    <t>#12 村上 崚久</t>
   </si>
   <si>
     <t>シートBT</t>
@@ -2760,7 +2763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BS322"/>
+  <dimension ref="A1:BS336"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:71">
@@ -3118,7 +3121,7 @@
         <v>798</v>
       </c>
       <c r="BR2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="3" spans="1:71">
@@ -3261,7 +3264,7 @@
         <v>798</v>
       </c>
       <c r="BR3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="4" spans="1:71">
@@ -3404,7 +3407,7 @@
         <v>798</v>
       </c>
       <c r="BR4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="5" spans="1:71">
@@ -3547,7 +3550,7 @@
         <v>798</v>
       </c>
       <c r="BR5" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="6" spans="1:71">
@@ -3690,7 +3693,7 @@
         <v>798</v>
       </c>
       <c r="BR6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="7" spans="1:71">
@@ -3833,7 +3836,7 @@
         <v>798</v>
       </c>
       <c r="BR7" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="8" spans="1:71">
@@ -3976,7 +3979,7 @@
         <v>798</v>
       </c>
       <c r="BR8" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="9" spans="1:71">
@@ -4119,7 +4122,7 @@
         <v>798</v>
       </c>
       <c r="BR9" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="10" spans="1:71">
@@ -4262,7 +4265,7 @@
         <v>798</v>
       </c>
       <c r="BR10" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="11" spans="1:71">
@@ -4438,7 +4441,7 @@
         <v>798</v>
       </c>
       <c r="BR11" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="12" spans="1:71">
@@ -4581,7 +4584,7 @@
         <v>798</v>
       </c>
       <c r="BR12" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="13" spans="1:71">
@@ -4718,7 +4721,7 @@
         <v>798</v>
       </c>
       <c r="BR13" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="14" spans="1:71">
@@ -4861,7 +4864,7 @@
         <v>798</v>
       </c>
       <c r="BR14" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="15" spans="1:71">
@@ -5004,7 +5007,7 @@
         <v>798</v>
       </c>
       <c r="BR15" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="16" spans="1:71">
@@ -5144,7 +5147,7 @@
         <v>798</v>
       </c>
       <c r="BR16" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="17" spans="1:70">
@@ -5284,7 +5287,7 @@
         <v>798</v>
       </c>
       <c r="BR17" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="18" spans="1:70">
@@ -5424,7 +5427,7 @@
         <v>798</v>
       </c>
       <c r="BR18" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="19" spans="1:70">
@@ -5567,7 +5570,7 @@
         <v>798</v>
       </c>
       <c r="BR19" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="20" spans="1:70">
@@ -5710,7 +5713,7 @@
         <v>798</v>
       </c>
       <c r="BR20" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="21" spans="1:70">
@@ -5853,7 +5856,7 @@
         <v>798</v>
       </c>
       <c r="BR21" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="22" spans="1:70">
@@ -6026,7 +6029,7 @@
         <v>798</v>
       </c>
       <c r="BR22" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="23" spans="1:70">
@@ -6169,7 +6172,7 @@
         <v>798</v>
       </c>
       <c r="BR23" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="24" spans="1:70">
@@ -6309,7 +6312,7 @@
         <v>798</v>
       </c>
       <c r="BR24" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="25" spans="1:70">
@@ -6452,7 +6455,7 @@
         <v>798</v>
       </c>
       <c r="BR25" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="26" spans="1:70">
@@ -6595,7 +6598,7 @@
         <v>798</v>
       </c>
       <c r="BR26" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="27" spans="1:70">
@@ -6738,7 +6741,7 @@
         <v>798</v>
       </c>
       <c r="BR27" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="28" spans="1:70">
@@ -6881,7 +6884,7 @@
         <v>798</v>
       </c>
       <c r="BR28" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="29" spans="1:70">
@@ -7024,7 +7027,7 @@
         <v>798</v>
       </c>
       <c r="BR29" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="30" spans="1:70">
@@ -7161,7 +7164,7 @@
         <v>798</v>
       </c>
       <c r="BR30" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="31" spans="1:70">
@@ -7304,7 +7307,7 @@
         <v>798</v>
       </c>
       <c r="BR31" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="32" spans="1:70">
@@ -7447,7 +7450,7 @@
         <v>798</v>
       </c>
       <c r="BR32" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="33" spans="1:71">
@@ -7587,7 +7590,7 @@
         <v>798</v>
       </c>
       <c r="BR33" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="34" spans="1:71">
@@ -7721,10 +7724,10 @@
         <v>798</v>
       </c>
       <c r="BR34" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS34" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="35" spans="1:71">
@@ -7858,10 +7861,10 @@
         <v>798</v>
       </c>
       <c r="BR35" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS35" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="36" spans="1:71">
@@ -7995,10 +7998,10 @@
         <v>798</v>
       </c>
       <c r="BR36" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS36" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="37" spans="1:71">
@@ -8132,10 +8135,10 @@
         <v>798</v>
       </c>
       <c r="BR37" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS37" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="38" spans="1:71">
@@ -8269,10 +8272,10 @@
         <v>798</v>
       </c>
       <c r="BR38" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS38" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="39" spans="1:71">
@@ -8406,10 +8409,10 @@
         <v>798</v>
       </c>
       <c r="BR39" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS39" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="40" spans="1:71">
@@ -8543,10 +8546,10 @@
         <v>798</v>
       </c>
       <c r="BR40" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS40" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="41" spans="1:71">
@@ -8680,10 +8683,10 @@
         <v>798</v>
       </c>
       <c r="BR41" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS41" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="42" spans="1:71">
@@ -8817,10 +8820,10 @@
         <v>798</v>
       </c>
       <c r="BR42" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS42" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="43" spans="1:71">
@@ -8954,10 +8957,10 @@
         <v>798</v>
       </c>
       <c r="BR43" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS43" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="44" spans="1:71">
@@ -9091,10 +9094,10 @@
         <v>798</v>
       </c>
       <c r="BR44" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS44" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="45" spans="1:71">
@@ -9228,10 +9231,10 @@
         <v>798</v>
       </c>
       <c r="BR45" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS45" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="46" spans="1:71">
@@ -9365,10 +9368,10 @@
         <v>798</v>
       </c>
       <c r="BR46" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS46" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="47" spans="1:71">
@@ -9502,10 +9505,10 @@
         <v>798</v>
       </c>
       <c r="BR47" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS47" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="48" spans="1:71">
@@ -9639,10 +9642,10 @@
         <v>798</v>
       </c>
       <c r="BR48" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS48" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="49" spans="1:71">
@@ -9776,10 +9779,10 @@
         <v>798</v>
       </c>
       <c r="BR49" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS49" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="50" spans="1:71">
@@ -9913,10 +9916,10 @@
         <v>798</v>
       </c>
       <c r="BR50" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS50" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="51" spans="1:71">
@@ -10050,10 +10053,10 @@
         <v>798</v>
       </c>
       <c r="BR51" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS51" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="52" spans="1:71">
@@ -10187,10 +10190,10 @@
         <v>798</v>
       </c>
       <c r="BR52" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS52" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="53" spans="1:71">
@@ -10324,10 +10327,10 @@
         <v>798</v>
       </c>
       <c r="BR53" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS53" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="54" spans="1:71">
@@ -10461,10 +10464,10 @@
         <v>798</v>
       </c>
       <c r="BR54" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS54" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="55" spans="1:71">
@@ -10598,10 +10601,10 @@
         <v>798</v>
       </c>
       <c r="BR55" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS55" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="56" spans="1:71">
@@ -10735,10 +10738,10 @@
         <v>798</v>
       </c>
       <c r="BR56" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS56" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="57" spans="1:71">
@@ -10872,10 +10875,10 @@
         <v>798</v>
       </c>
       <c r="BR57" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS57" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="58" spans="1:71">
@@ -11009,10 +11012,10 @@
         <v>798</v>
       </c>
       <c r="BR58" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS58" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="59" spans="1:71">
@@ -11146,10 +11149,10 @@
         <v>798</v>
       </c>
       <c r="BR59" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS59" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="60" spans="1:71">
@@ -11283,10 +11286,10 @@
         <v>798</v>
       </c>
       <c r="BR60" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS60" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="61" spans="1:71">
@@ -11420,10 +11423,10 @@
         <v>798</v>
       </c>
       <c r="BR61" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS61" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="62" spans="1:71">
@@ -11557,10 +11560,10 @@
         <v>798</v>
       </c>
       <c r="BR62" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS62" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="63" spans="1:71">
@@ -11694,10 +11697,10 @@
         <v>798</v>
       </c>
       <c r="BR63" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS63" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="64" spans="1:71">
@@ -11831,10 +11834,10 @@
         <v>798</v>
       </c>
       <c r="BR64" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS64" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="65" spans="1:71">
@@ -11968,10 +11971,10 @@
         <v>798</v>
       </c>
       <c r="BR65" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS65" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="66" spans="1:71">
@@ -12105,10 +12108,10 @@
         <v>798</v>
       </c>
       <c r="BR66" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS66" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="67" spans="1:71">
@@ -12242,10 +12245,10 @@
         <v>798</v>
       </c>
       <c r="BR67" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS67" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="68" spans="1:71">
@@ -12379,10 +12382,10 @@
         <v>798</v>
       </c>
       <c r="BR68" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS68" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="69" spans="1:71">
@@ -12516,10 +12519,10 @@
         <v>798</v>
       </c>
       <c r="BR69" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS69" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="70" spans="1:71">
@@ -12653,10 +12656,10 @@
         <v>798</v>
       </c>
       <c r="BR70" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS70" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="71" spans="1:71">
@@ -12790,10 +12793,10 @@
         <v>798</v>
       </c>
       <c r="BR71" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS71" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="72" spans="1:71">
@@ -12927,10 +12930,10 @@
         <v>798</v>
       </c>
       <c r="BR72" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS72" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="73" spans="1:71">
@@ -13064,10 +13067,10 @@
         <v>798</v>
       </c>
       <c r="BR73" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS73" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="74" spans="1:71">
@@ -13201,10 +13204,10 @@
         <v>798</v>
       </c>
       <c r="BR74" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS74" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="75" spans="1:71">
@@ -13338,10 +13341,10 @@
         <v>798</v>
       </c>
       <c r="BR75" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS75" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="76" spans="1:71">
@@ -13490,10 +13493,10 @@
         <v>798</v>
       </c>
       <c r="BR76" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS76" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="77" spans="1:71">
@@ -13627,10 +13630,10 @@
         <v>798</v>
       </c>
       <c r="BR77" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS77" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="78" spans="1:71">
@@ -13764,10 +13767,10 @@
         <v>798</v>
       </c>
       <c r="BR78" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS78" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="79" spans="1:71">
@@ -13901,10 +13904,10 @@
         <v>798</v>
       </c>
       <c r="BR79" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS79" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="80" spans="1:71">
@@ -14038,10 +14041,10 @@
         <v>798</v>
       </c>
       <c r="BR80" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS80" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="81" spans="1:71">
@@ -14175,10 +14178,10 @@
         <v>798</v>
       </c>
       <c r="BR81" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS81" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="82" spans="1:71">
@@ -14312,10 +14315,10 @@
         <v>798</v>
       </c>
       <c r="BR82" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS82" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="83" spans="1:71">
@@ -14449,10 +14452,10 @@
         <v>798</v>
       </c>
       <c r="BR83" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS83" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="84" spans="1:71">
@@ -14580,10 +14583,10 @@
         <v>798</v>
       </c>
       <c r="BR84" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS84" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="85" spans="1:71">
@@ -14717,10 +14720,10 @@
         <v>799</v>
       </c>
       <c r="BR85" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS85" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="86" spans="1:71">
@@ -14854,10 +14857,10 @@
         <v>799</v>
       </c>
       <c r="BR86" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS86" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="87" spans="1:71">
@@ -14991,10 +14994,10 @@
         <v>799</v>
       </c>
       <c r="BR87" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS87" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="88" spans="1:71">
@@ -15128,10 +15131,10 @@
         <v>799</v>
       </c>
       <c r="BR88" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS88" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="89" spans="1:71">
@@ -15265,10 +15268,10 @@
         <v>799</v>
       </c>
       <c r="BR89" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS89" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="90" spans="1:71">
@@ -15402,10 +15405,10 @@
         <v>799</v>
       </c>
       <c r="BR90" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS90" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="91" spans="1:71">
@@ -15539,10 +15542,10 @@
         <v>799</v>
       </c>
       <c r="BR91" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS91" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="92" spans="1:71">
@@ -15676,10 +15679,10 @@
         <v>799</v>
       </c>
       <c r="BR92" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS92" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="93" spans="1:71">
@@ -15813,10 +15816,10 @@
         <v>799</v>
       </c>
       <c r="BR93" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS93" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="94" spans="1:71">
@@ -15950,10 +15953,10 @@
         <v>799</v>
       </c>
       <c r="BR94" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS94" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="95" spans="1:71">
@@ -16087,10 +16090,10 @@
         <v>799</v>
       </c>
       <c r="BR95" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS95" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="96" spans="1:71">
@@ -16224,10 +16227,10 @@
         <v>799</v>
       </c>
       <c r="BR96" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS96" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="97" spans="1:71">
@@ -16361,10 +16364,10 @@
         <v>799</v>
       </c>
       <c r="BR97" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS97" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="98" spans="1:71">
@@ -16498,10 +16501,10 @@
         <v>799</v>
       </c>
       <c r="BR98" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS98" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="99" spans="1:71">
@@ -16635,10 +16638,10 @@
         <v>799</v>
       </c>
       <c r="BR99" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS99" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="100" spans="1:71">
@@ -16772,10 +16775,10 @@
         <v>799</v>
       </c>
       <c r="BR100" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS100" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="101" spans="1:71">
@@ -16909,10 +16912,10 @@
         <v>799</v>
       </c>
       <c r="BR101" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS101" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="102" spans="1:71">
@@ -17046,10 +17049,10 @@
         <v>799</v>
       </c>
       <c r="BR102" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS102" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="103" spans="1:71">
@@ -17183,10 +17186,10 @@
         <v>799</v>
       </c>
       <c r="BR103" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS103" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="104" spans="1:71">
@@ -17320,10 +17323,10 @@
         <v>799</v>
       </c>
       <c r="BR104" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS104" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="105" spans="1:71">
@@ -17457,10 +17460,10 @@
         <v>799</v>
       </c>
       <c r="BR105" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS105" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="106" spans="1:71">
@@ -17594,10 +17597,10 @@
         <v>799</v>
       </c>
       <c r="BR106" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS106" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="107" spans="1:71">
@@ -17731,10 +17734,10 @@
         <v>799</v>
       </c>
       <c r="BR107" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS107" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="108" spans="1:71">
@@ -17868,10 +17871,10 @@
         <v>799</v>
       </c>
       <c r="BR108" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS108" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="109" spans="1:71">
@@ -18005,10 +18008,10 @@
         <v>799</v>
       </c>
       <c r="BR109" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS109" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="110" spans="1:71">
@@ -18142,10 +18145,10 @@
         <v>799</v>
       </c>
       <c r="BR110" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS110" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="111" spans="1:71">
@@ -18279,10 +18282,10 @@
         <v>799</v>
       </c>
       <c r="BR111" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS111" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="112" spans="1:71">
@@ -18416,10 +18419,10 @@
         <v>799</v>
       </c>
       <c r="BR112" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS112" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="113" spans="1:71">
@@ -18553,10 +18556,10 @@
         <v>799</v>
       </c>
       <c r="BR113" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS113" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="114" spans="1:71">
@@ -18690,10 +18693,10 @@
         <v>799</v>
       </c>
       <c r="BR114" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS114" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="115" spans="1:71">
@@ -18827,10 +18830,10 @@
         <v>799</v>
       </c>
       <c r="BR115" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS115" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="116" spans="1:71">
@@ -18964,10 +18967,10 @@
         <v>799</v>
       </c>
       <c r="BR116" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS116" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="117" spans="1:71">
@@ -19101,10 +19104,10 @@
         <v>799</v>
       </c>
       <c r="BR117" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS117" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="118" spans="1:71">
@@ -19238,10 +19241,10 @@
         <v>799</v>
       </c>
       <c r="BR118" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS118" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="119" spans="1:71">
@@ -19375,10 +19378,10 @@
         <v>799</v>
       </c>
       <c r="BR119" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS119" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="120" spans="1:71">
@@ -19512,10 +19515,10 @@
         <v>799</v>
       </c>
       <c r="BR120" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS120" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="121" spans="1:71">
@@ -19649,10 +19652,10 @@
         <v>799</v>
       </c>
       <c r="BR121" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS121" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="122" spans="1:71">
@@ -19786,10 +19789,10 @@
         <v>799</v>
       </c>
       <c r="BR122" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS122" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="123" spans="1:71">
@@ -19923,10 +19926,10 @@
         <v>799</v>
       </c>
       <c r="BR123" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS123" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="124" spans="1:71">
@@ -20060,10 +20063,10 @@
         <v>799</v>
       </c>
       <c r="BR124" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS124" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="125" spans="1:71">
@@ -20197,10 +20200,10 @@
         <v>799</v>
       </c>
       <c r="BR125" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS125" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="126" spans="1:71">
@@ -20334,10 +20337,10 @@
         <v>799</v>
       </c>
       <c r="BR126" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS126" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="127" spans="1:71">
@@ -20471,10 +20474,10 @@
         <v>799</v>
       </c>
       <c r="BR127" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS127" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="128" spans="1:71">
@@ -20608,10 +20611,10 @@
         <v>799</v>
       </c>
       <c r="BR128" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS128" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="129" spans="1:71">
@@ -20745,10 +20748,10 @@
         <v>799</v>
       </c>
       <c r="BR129" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS129" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="130" spans="1:71">
@@ -20882,10 +20885,10 @@
         <v>799</v>
       </c>
       <c r="BR130" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS130" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="131" spans="1:71">
@@ -21019,10 +21022,10 @@
         <v>799</v>
       </c>
       <c r="BR131" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS131" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="132" spans="1:71">
@@ -21156,10 +21159,10 @@
         <v>799</v>
       </c>
       <c r="BR132" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS132" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="133" spans="1:71">
@@ -21293,10 +21296,10 @@
         <v>799</v>
       </c>
       <c r="BR133" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS133" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="134" spans="1:71">
@@ -21430,10 +21433,10 @@
         <v>799</v>
       </c>
       <c r="BR134" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS134" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="135" spans="1:71">
@@ -21567,10 +21570,10 @@
         <v>799</v>
       </c>
       <c r="BR135" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS135" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="136" spans="1:71">
@@ -21704,10 +21707,10 @@
         <v>799</v>
       </c>
       <c r="BR136" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS136" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="137" spans="1:71">
@@ -21841,10 +21844,10 @@
         <v>799</v>
       </c>
       <c r="BR137" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS137" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="138" spans="1:71">
@@ -21978,10 +21981,10 @@
         <v>799</v>
       </c>
       <c r="BR138" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS138" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="139" spans="1:71">
@@ -22115,10 +22118,10 @@
         <v>799</v>
       </c>
       <c r="BR139" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS139" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="140" spans="1:71">
@@ -22252,10 +22255,10 @@
         <v>799</v>
       </c>
       <c r="BR140" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS140" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="141" spans="1:71">
@@ -22389,10 +22392,10 @@
         <v>799</v>
       </c>
       <c r="BR141" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS141" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="142" spans="1:71">
@@ -22526,10 +22529,10 @@
         <v>799</v>
       </c>
       <c r="BR142" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS142" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="143" spans="1:71">
@@ -22663,10 +22666,10 @@
         <v>799</v>
       </c>
       <c r="BR143" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS143" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="144" spans="1:71">
@@ -22800,10 +22803,10 @@
         <v>800</v>
       </c>
       <c r="BR144" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS144" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="145" spans="1:71">
@@ -22937,10 +22940,10 @@
         <v>800</v>
       </c>
       <c r="BR145" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS145" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="146" spans="1:71">
@@ -23074,10 +23077,10 @@
         <v>800</v>
       </c>
       <c r="BR146" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS146" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="147" spans="1:71">
@@ -23211,10 +23214,10 @@
         <v>800</v>
       </c>
       <c r="BR147" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS147" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="148" spans="1:71">
@@ -23348,10 +23351,10 @@
         <v>800</v>
       </c>
       <c r="BR148" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS148" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="149" spans="1:71">
@@ -23485,10 +23488,10 @@
         <v>800</v>
       </c>
       <c r="BR149" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS149" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="150" spans="1:71">
@@ -23622,10 +23625,10 @@
         <v>800</v>
       </c>
       <c r="BR150" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS150" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="151" spans="1:71">
@@ -23759,10 +23762,10 @@
         <v>800</v>
       </c>
       <c r="BR151" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS151" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="152" spans="1:71">
@@ -23896,10 +23899,10 @@
         <v>800</v>
       </c>
       <c r="BR152" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS152" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="153" spans="1:71">
@@ -24033,10 +24036,10 @@
         <v>800</v>
       </c>
       <c r="BR153" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS153" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="154" spans="1:71">
@@ -24170,10 +24173,10 @@
         <v>800</v>
       </c>
       <c r="BR154" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS154" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="155" spans="1:71">
@@ -24307,10 +24310,10 @@
         <v>800</v>
       </c>
       <c r="BR155" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS155" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="156" spans="1:71">
@@ -24444,10 +24447,10 @@
         <v>800</v>
       </c>
       <c r="BR156" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS156" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="157" spans="1:71">
@@ -24581,10 +24584,10 @@
         <v>800</v>
       </c>
       <c r="BR157" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS157" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="158" spans="1:71">
@@ -24718,10 +24721,10 @@
         <v>800</v>
       </c>
       <c r="BR158" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS158" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="159" spans="1:71">
@@ -24855,10 +24858,10 @@
         <v>800</v>
       </c>
       <c r="BR159" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS159" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="160" spans="1:71">
@@ -24992,10 +24995,10 @@
         <v>800</v>
       </c>
       <c r="BR160" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS160" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="161" spans="1:71">
@@ -25129,10 +25132,10 @@
         <v>800</v>
       </c>
       <c r="BR161" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS161" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="162" spans="1:71">
@@ -25266,10 +25269,10 @@
         <v>800</v>
       </c>
       <c r="BR162" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS162" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="163" spans="1:71">
@@ -25403,10 +25406,10 @@
         <v>800</v>
       </c>
       <c r="BR163" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS163" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="164" spans="1:71">
@@ -25540,10 +25543,10 @@
         <v>800</v>
       </c>
       <c r="BR164" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS164" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="165" spans="1:71">
@@ -25677,10 +25680,10 @@
         <v>800</v>
       </c>
       <c r="BR165" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS165" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="166" spans="1:71">
@@ -25814,10 +25817,10 @@
         <v>800</v>
       </c>
       <c r="BR166" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS166" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="167" spans="1:71">
@@ -25951,10 +25954,10 @@
         <v>800</v>
       </c>
       <c r="BR167" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS167" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="168" spans="1:71">
@@ -26088,10 +26091,10 @@
         <v>800</v>
       </c>
       <c r="BR168" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS168" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="169" spans="1:71">
@@ -26225,10 +26228,10 @@
         <v>800</v>
       </c>
       <c r="BR169" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS169" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="170" spans="1:71">
@@ -26362,10 +26365,10 @@
         <v>800</v>
       </c>
       <c r="BR170" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS170" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="171" spans="1:71">
@@ -26499,10 +26502,10 @@
         <v>800</v>
       </c>
       <c r="BR171" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS171" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="172" spans="1:71">
@@ -26636,10 +26639,10 @@
         <v>800</v>
       </c>
       <c r="BR172" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS172" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="173" spans="1:71">
@@ -26773,10 +26776,10 @@
         <v>800</v>
       </c>
       <c r="BR173" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS173" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="174" spans="1:71">
@@ -26901,10 +26904,10 @@
         <v>800</v>
       </c>
       <c r="BR174" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS174" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="175" spans="1:71">
@@ -27029,10 +27032,10 @@
         <v>800</v>
       </c>
       <c r="BR175" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS175" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="176" spans="1:71">
@@ -27166,10 +27169,10 @@
         <v>800</v>
       </c>
       <c r="BR176" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS176" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="177" spans="1:71">
@@ -27303,10 +27306,10 @@
         <v>800</v>
       </c>
       <c r="BR177" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS177" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="178" spans="1:71">
@@ -27440,10 +27443,10 @@
         <v>800</v>
       </c>
       <c r="BR178" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS178" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="179" spans="1:71">
@@ -27568,10 +27571,10 @@
         <v>800</v>
       </c>
       <c r="BR179" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS179" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="180" spans="1:71">
@@ -27705,10 +27708,10 @@
         <v>800</v>
       </c>
       <c r="BR180" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS180" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="181" spans="1:71">
@@ -27842,10 +27845,10 @@
         <v>800</v>
       </c>
       <c r="BR181" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS181" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="182" spans="1:71">
@@ -27979,10 +27982,10 @@
         <v>800</v>
       </c>
       <c r="BR182" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS182" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="183" spans="1:71">
@@ -28107,10 +28110,10 @@
         <v>800</v>
       </c>
       <c r="BR183" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS183" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="184" spans="1:71">
@@ -28244,10 +28247,10 @@
         <v>800</v>
       </c>
       <c r="BR184" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS184" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="185" spans="1:71">
@@ -28381,10 +28384,10 @@
         <v>800</v>
       </c>
       <c r="BR185" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS185" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="186" spans="1:71">
@@ -28518,10 +28521,10 @@
         <v>800</v>
       </c>
       <c r="BR186" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS186" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="187" spans="1:71">
@@ -28655,10 +28658,10 @@
         <v>800</v>
       </c>
       <c r="BR187" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS187" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="188" spans="1:71">
@@ -28792,10 +28795,10 @@
         <v>800</v>
       </c>
       <c r="BR188" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS188" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="189" spans="1:71">
@@ -28929,10 +28932,10 @@
         <v>800</v>
       </c>
       <c r="BR189" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS189" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="190" spans="1:71">
@@ -29066,10 +29069,10 @@
         <v>800</v>
       </c>
       <c r="BR190" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS190" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="191" spans="1:71">
@@ -29203,10 +29206,10 @@
         <v>800</v>
       </c>
       <c r="BR191" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS191" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="192" spans="1:71">
@@ -29340,10 +29343,10 @@
         <v>800</v>
       </c>
       <c r="BR192" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS192" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="193" spans="1:71">
@@ -29477,10 +29480,10 @@
         <v>800</v>
       </c>
       <c r="BR193" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS193" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="194" spans="1:71">
@@ -29605,10 +29608,10 @@
         <v>800</v>
       </c>
       <c r="BR194" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS194" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="195" spans="1:71">
@@ -29733,10 +29736,10 @@
         <v>800</v>
       </c>
       <c r="BR195" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS195" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="196" spans="1:71">
@@ -29861,10 +29864,10 @@
         <v>800</v>
       </c>
       <c r="BR196" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS196" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="197" spans="1:71">
@@ -29989,10 +29992,10 @@
         <v>800</v>
       </c>
       <c r="BR197" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS197" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="198" spans="1:71">
@@ -30117,10 +30120,10 @@
         <v>800</v>
       </c>
       <c r="BR198" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS198" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="199" spans="1:71">
@@ -30245,10 +30248,10 @@
         <v>800</v>
       </c>
       <c r="BR199" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS199" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="200" spans="1:71">
@@ -30373,10 +30376,10 @@
         <v>800</v>
       </c>
       <c r="BR200" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS200" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="201" spans="1:71">
@@ -30501,10 +30504,10 @@
         <v>800</v>
       </c>
       <c r="BR201" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS201" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="202" spans="1:71">
@@ -30629,10 +30632,10 @@
         <v>800</v>
       </c>
       <c r="BR202" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS202" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="203" spans="1:71">
@@ -30757,10 +30760,10 @@
         <v>800</v>
       </c>
       <c r="BR203" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS203" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="204" spans="1:71">
@@ -30885,10 +30888,10 @@
         <v>800</v>
       </c>
       <c r="BR204" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS204" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="205" spans="1:71">
@@ -31013,10 +31016,10 @@
         <v>800</v>
       </c>
       <c r="BR205" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS205" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="206" spans="1:71">
@@ -31150,10 +31153,10 @@
         <v>800</v>
       </c>
       <c r="BR206" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS206" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="207" spans="1:71">
@@ -31287,10 +31290,10 @@
         <v>800</v>
       </c>
       <c r="BR207" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS207" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="208" spans="1:71">
@@ -31424,10 +31427,10 @@
         <v>800</v>
       </c>
       <c r="BR208" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS208" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="209" spans="1:71">
@@ -31561,10 +31564,10 @@
         <v>800</v>
       </c>
       <c r="BR209" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS209" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="210" spans="1:71">
@@ -31698,10 +31701,10 @@
         <v>801</v>
       </c>
       <c r="BR210" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS210" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="211" spans="1:71">
@@ -31835,10 +31838,10 @@
         <v>801</v>
       </c>
       <c r="BR211" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS211" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="212" spans="1:71">
@@ -31972,10 +31975,10 @@
         <v>801</v>
       </c>
       <c r="BR212" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS212" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="213" spans="1:71">
@@ -32109,10 +32112,10 @@
         <v>801</v>
       </c>
       <c r="BR213" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS213" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="214" spans="1:71">
@@ -32219,10 +32222,10 @@
         <v>801</v>
       </c>
       <c r="BR214" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS214" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="215" spans="1:71">
@@ -32356,10 +32359,10 @@
         <v>801</v>
       </c>
       <c r="BR215" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS215" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="216" spans="1:71">
@@ -32493,10 +32496,10 @@
         <v>801</v>
       </c>
       <c r="BR216" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS216" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="217" spans="1:71">
@@ -32630,10 +32633,10 @@
         <v>801</v>
       </c>
       <c r="BR217" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS217" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="218" spans="1:71">
@@ -32767,10 +32770,10 @@
         <v>801</v>
       </c>
       <c r="BR218" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS218" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="219" spans="1:71">
@@ -32904,10 +32907,10 @@
         <v>801</v>
       </c>
       <c r="BR219" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS219" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="220" spans="1:71">
@@ -33041,10 +33044,10 @@
         <v>801</v>
       </c>
       <c r="BR220" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS220" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="221" spans="1:71">
@@ -33178,10 +33181,10 @@
         <v>801</v>
       </c>
       <c r="BR221" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS221" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="222" spans="1:71">
@@ -33294,10 +33297,10 @@
         <v>801</v>
       </c>
       <c r="BR222" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS222" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="223" spans="1:71">
@@ -33431,10 +33434,10 @@
         <v>801</v>
       </c>
       <c r="BR223" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS223" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="224" spans="1:71">
@@ -33568,10 +33571,10 @@
         <v>801</v>
       </c>
       <c r="BR224" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS224" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="225" spans="1:71">
@@ -33705,10 +33708,10 @@
         <v>801</v>
       </c>
       <c r="BR225" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS225" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="226" spans="1:71">
@@ -33842,10 +33845,10 @@
         <v>801</v>
       </c>
       <c r="BR226" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS226" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="227" spans="1:71">
@@ -33979,10 +33982,10 @@
         <v>801</v>
       </c>
       <c r="BR227" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS227" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="228" spans="1:71">
@@ -34116,10 +34119,10 @@
         <v>801</v>
       </c>
       <c r="BR228" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS228" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="229" spans="1:71">
@@ -34253,10 +34256,10 @@
         <v>801</v>
       </c>
       <c r="BR229" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS229" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="230" spans="1:71">
@@ -34390,10 +34393,10 @@
         <v>801</v>
       </c>
       <c r="BR230" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS230" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="231" spans="1:71">
@@ -34527,10 +34530,10 @@
         <v>801</v>
       </c>
       <c r="BR231" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS231" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="232" spans="1:71">
@@ -34664,10 +34667,10 @@
         <v>801</v>
       </c>
       <c r="BR232" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS232" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="233" spans="1:71">
@@ -34801,10 +34804,10 @@
         <v>801</v>
       </c>
       <c r="BR233" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS233" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="234" spans="1:71">
@@ -34938,10 +34941,10 @@
         <v>801</v>
       </c>
       <c r="BR234" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS234" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="235" spans="1:71">
@@ -35075,10 +35078,10 @@
         <v>801</v>
       </c>
       <c r="BR235" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS235" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="236" spans="1:71">
@@ -35212,10 +35215,10 @@
         <v>801</v>
       </c>
       <c r="BR236" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS236" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="237" spans="1:71">
@@ -35349,10 +35352,10 @@
         <v>801</v>
       </c>
       <c r="BR237" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS237" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="238" spans="1:71">
@@ -35486,10 +35489,10 @@
         <v>801</v>
       </c>
       <c r="BR238" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS238" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="239" spans="1:71">
@@ -35623,10 +35626,10 @@
         <v>801</v>
       </c>
       <c r="BR239" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS239" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="240" spans="1:71">
@@ -35760,10 +35763,10 @@
         <v>801</v>
       </c>
       <c r="BR240" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS240" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="241" spans="1:71">
@@ -35897,10 +35900,10 @@
         <v>801</v>
       </c>
       <c r="BR241" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS241" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="242" spans="1:71">
@@ -36034,10 +36037,10 @@
         <v>801</v>
       </c>
       <c r="BR242" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS242" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="243" spans="1:71">
@@ -36171,10 +36174,10 @@
         <v>801</v>
       </c>
       <c r="BR243" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS243" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="244" spans="1:71">
@@ -36308,10 +36311,10 @@
         <v>801</v>
       </c>
       <c r="BR244" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS244" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="245" spans="1:71">
@@ -36445,10 +36448,10 @@
         <v>801</v>
       </c>
       <c r="BR245" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS245" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="246" spans="1:71">
@@ -36582,10 +36585,10 @@
         <v>801</v>
       </c>
       <c r="BR246" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS246" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="247" spans="1:71">
@@ -36719,10 +36722,10 @@
         <v>801</v>
       </c>
       <c r="BR247" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS247" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="248" spans="1:71">
@@ -36856,10 +36859,10 @@
         <v>801</v>
       </c>
       <c r="BR248" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS248" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="249" spans="1:71">
@@ -36993,10 +36996,10 @@
         <v>801</v>
       </c>
       <c r="BR249" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS249" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="250" spans="1:71">
@@ -37130,10 +37133,10 @@
         <v>801</v>
       </c>
       <c r="BR250" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS250" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="251" spans="1:71">
@@ -37267,10 +37270,10 @@
         <v>801</v>
       </c>
       <c r="BR251" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS251" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="252" spans="1:71">
@@ -37404,10 +37407,10 @@
         <v>801</v>
       </c>
       <c r="BR252" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS252" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="253" spans="1:71">
@@ -37541,10 +37544,10 @@
         <v>801</v>
       </c>
       <c r="BR253" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS253" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="254" spans="1:71">
@@ -37678,10 +37681,10 @@
         <v>801</v>
       </c>
       <c r="BR254" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS254" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="255" spans="1:71">
@@ -37815,10 +37818,10 @@
         <v>801</v>
       </c>
       <c r="BR255" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS255" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="256" spans="1:71">
@@ -37952,10 +37955,10 @@
         <v>801</v>
       </c>
       <c r="BR256" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS256" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="257" spans="1:71">
@@ -38089,10 +38092,10 @@
         <v>801</v>
       </c>
       <c r="BR257" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="BS257" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="258" spans="1:71">
@@ -38235,10 +38238,10 @@
         <v>801</v>
       </c>
       <c r="BR258" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS258" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="259" spans="1:71">
@@ -38381,10 +38384,10 @@
         <v>801</v>
       </c>
       <c r="BR259" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS259" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="260" spans="1:71">
@@ -38527,10 +38530,10 @@
         <v>801</v>
       </c>
       <c r="BR260" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS260" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="261" spans="1:71">
@@ -38673,10 +38676,10 @@
         <v>801</v>
       </c>
       <c r="BR261" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS261" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="262" spans="1:71">
@@ -38819,10 +38822,10 @@
         <v>801</v>
       </c>
       <c r="BR262" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS262" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="263" spans="1:71">
@@ -38965,10 +38968,10 @@
         <v>801</v>
       </c>
       <c r="BR263" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS263" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="264" spans="1:71">
@@ -39111,10 +39114,10 @@
         <v>801</v>
       </c>
       <c r="BR264" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS264" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="265" spans="1:71">
@@ -39290,10 +39293,10 @@
         <v>801</v>
       </c>
       <c r="BR265" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS265" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="266" spans="1:71">
@@ -39436,10 +39439,10 @@
         <v>801</v>
       </c>
       <c r="BR266" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS266" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="267" spans="1:71">
@@ -39582,10 +39585,10 @@
         <v>801</v>
       </c>
       <c r="BR267" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS267" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="268" spans="1:71">
@@ -39728,10 +39731,10 @@
         <v>801</v>
       </c>
       <c r="BR268" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS268" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="269" spans="1:71">
@@ -39874,10 +39877,10 @@
         <v>801</v>
       </c>
       <c r="BR269" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS269" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="270" spans="1:71">
@@ -40020,10 +40023,10 @@
         <v>801</v>
       </c>
       <c r="BR270" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS270" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="271" spans="1:71">
@@ -40166,10 +40169,10 @@
         <v>801</v>
       </c>
       <c r="BR271" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS271" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="272" spans="1:71">
@@ -40312,10 +40315,10 @@
         <v>801</v>
       </c>
       <c r="BR272" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS272" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="273" spans="1:71">
@@ -40491,10 +40494,10 @@
         <v>801</v>
       </c>
       <c r="BR273" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS273" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="274" spans="1:71">
@@ -40670,10 +40673,10 @@
         <v>801</v>
       </c>
       <c r="BR274" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS274" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="275" spans="1:71">
@@ -40816,10 +40819,10 @@
         <v>801</v>
       </c>
       <c r="BR275" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS275" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="276" spans="1:71">
@@ -40962,10 +40965,10 @@
         <v>799</v>
       </c>
       <c r="BR276" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS276" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="277" spans="1:71">
@@ -41108,10 +41111,10 @@
         <v>799</v>
       </c>
       <c r="BR277" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS277" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="278" spans="1:71">
@@ -41287,10 +41290,10 @@
         <v>799</v>
       </c>
       <c r="BR278" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS278" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="279" spans="1:71">
@@ -41433,10 +41436,10 @@
         <v>799</v>
       </c>
       <c r="BR279" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS279" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="280" spans="1:71">
@@ -41579,10 +41582,10 @@
         <v>799</v>
       </c>
       <c r="BR280" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS280" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="281" spans="1:71">
@@ -41725,10 +41728,10 @@
         <v>799</v>
       </c>
       <c r="BR281" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS281" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="282" spans="1:71">
@@ -41865,10 +41868,10 @@
         <v>799</v>
       </c>
       <c r="BR282" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS282" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="283" spans="1:71">
@@ -42011,10 +42014,10 @@
         <v>799</v>
       </c>
       <c r="BR283" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS283" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="284" spans="1:71">
@@ -42184,10 +42187,10 @@
         <v>799</v>
       </c>
       <c r="BR284" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS284" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="285" spans="1:71">
@@ -42324,10 +42327,10 @@
         <v>799</v>
       </c>
       <c r="BR285" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS285" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="286" spans="1:71">
@@ -42470,10 +42473,10 @@
         <v>799</v>
       </c>
       <c r="BR286" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS286" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="287" spans="1:71">
@@ -42616,10 +42619,10 @@
         <v>799</v>
       </c>
       <c r="BR287" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS287" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="288" spans="1:71">
@@ -42762,10 +42765,10 @@
         <v>799</v>
       </c>
       <c r="BR288" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS288" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="289" spans="1:71">
@@ -42941,10 +42944,10 @@
         <v>799</v>
       </c>
       <c r="BR289" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS289" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="290" spans="1:71">
@@ -43087,10 +43090,10 @@
         <v>799</v>
       </c>
       <c r="BR290" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS290" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="291" spans="1:71">
@@ -43233,10 +43236,10 @@
         <v>799</v>
       </c>
       <c r="BR291" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS291" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="292" spans="1:71">
@@ -43379,10 +43382,10 @@
         <v>799</v>
       </c>
       <c r="BR292" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS292" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="293" spans="1:71">
@@ -43525,10 +43528,10 @@
         <v>799</v>
       </c>
       <c r="BR293" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS293" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="294" spans="1:71">
@@ -43704,10 +43707,10 @@
         <v>799</v>
       </c>
       <c r="BR294" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS294" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="295" spans="1:71">
@@ -43850,10 +43853,10 @@
         <v>799</v>
       </c>
       <c r="BR295" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS295" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="296" spans="1:71">
@@ -43996,10 +43999,10 @@
         <v>799</v>
       </c>
       <c r="BR296" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS296" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="297" spans="1:71">
@@ -44142,10 +44145,10 @@
         <v>799</v>
       </c>
       <c r="BR297" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS297" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="298" spans="1:71">
@@ -44288,10 +44291,10 @@
         <v>799</v>
       </c>
       <c r="BR298" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS298" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="299" spans="1:71">
@@ -44467,10 +44470,10 @@
         <v>799</v>
       </c>
       <c r="BR299" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS299" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="300" spans="1:71">
@@ -44613,10 +44616,10 @@
         <v>799</v>
       </c>
       <c r="BR300" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS300" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="301" spans="1:71">
@@ -44759,10 +44762,10 @@
         <v>799</v>
       </c>
       <c r="BR301" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS301" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="302" spans="1:71">
@@ -44905,10 +44908,10 @@
         <v>799</v>
       </c>
       <c r="BR302" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS302" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="303" spans="1:71">
@@ -45051,10 +45054,10 @@
         <v>799</v>
       </c>
       <c r="BR303" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS303" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="304" spans="1:71">
@@ -45197,10 +45200,10 @@
         <v>799</v>
       </c>
       <c r="BR304" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS304" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="305" spans="1:71">
@@ -45346,10 +45349,10 @@
         <v>799</v>
       </c>
       <c r="BR305" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS305" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="306" spans="1:71">
@@ -45462,10 +45465,10 @@
         <v>799</v>
       </c>
       <c r="BR306" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS306" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="307" spans="1:71">
@@ -45608,10 +45611,10 @@
         <v>799</v>
       </c>
       <c r="BR307" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS307" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="308" spans="1:71">
@@ -45748,10 +45751,10 @@
         <v>799</v>
       </c>
       <c r="BR308" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS308" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="309" spans="1:71">
@@ -45864,10 +45867,10 @@
         <v>798</v>
       </c>
       <c r="BR309" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS309" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="310" spans="1:71">
@@ -46010,10 +46013,10 @@
         <v>798</v>
       </c>
       <c r="BR310" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS310" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="311" spans="1:71">
@@ -46156,10 +46159,10 @@
         <v>798</v>
       </c>
       <c r="BR311" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS311" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="312" spans="1:71">
@@ -46302,10 +46305,10 @@
         <v>798</v>
       </c>
       <c r="BR312" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS312" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="313" spans="1:71">
@@ -46448,10 +46451,10 @@
         <v>798</v>
       </c>
       <c r="BR313" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS313" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="314" spans="1:71">
@@ -46597,10 +46600,10 @@
         <v>798</v>
       </c>
       <c r="BR314" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS314" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="315" spans="1:71">
@@ -46743,10 +46746,10 @@
         <v>798</v>
       </c>
       <c r="BR315" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS315" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="316" spans="1:71">
@@ -46889,10 +46892,10 @@
         <v>798</v>
       </c>
       <c r="BR316" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS316" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="317" spans="1:71">
@@ -47035,10 +47038,10 @@
         <v>798</v>
       </c>
       <c r="BR317" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS317" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="318" spans="1:71">
@@ -47181,10 +47184,10 @@
         <v>798</v>
       </c>
       <c r="BR318" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS318" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="319" spans="1:71">
@@ -47330,10 +47333,10 @@
         <v>798</v>
       </c>
       <c r="BR319" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS319" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="320" spans="1:71">
@@ -47476,10 +47479,10 @@
         <v>798</v>
       </c>
       <c r="BR320" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS320" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="321" spans="1:71">
@@ -47655,10 +47658,10 @@
         <v>798</v>
       </c>
       <c r="BR321" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="BS321" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="322" spans="1:71">
@@ -47801,10 +47804,2063 @@
         <v>798</v>
       </c>
       <c r="BR322" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS322" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="323" spans="1:71">
+      <c r="A323">
+        <v>153</v>
+      </c>
+      <c r="B323" t="s">
+        <v>74</v>
+      </c>
+      <c r="C323" t="s">
+        <v>382</v>
+      </c>
+      <c r="D323" t="s">
+        <v>400</v>
+      </c>
+      <c r="E323">
+        <v>1000542960</v>
+      </c>
+      <c r="F323" t="s">
+        <v>401</v>
+      </c>
+      <c r="I323" t="s">
+        <v>408</v>
+      </c>
+      <c r="J323" t="s">
+        <v>410</v>
+      </c>
+      <c r="L323">
+        <v>120.27126</v>
+      </c>
+      <c r="M323">
+        <v>-2.446958349</v>
+      </c>
+      <c r="N323">
+        <v>-3.692497795</v>
+      </c>
+      <c r="O323">
+        <v>1151.427703</v>
+      </c>
+      <c r="P323">
+        <v>255.6767422</v>
+      </c>
+      <c r="Q323" t="s">
+        <v>429</v>
+      </c>
+      <c r="R323">
+        <v>1.629951432</v>
+      </c>
+      <c r="S323">
+        <v>0.474173502</v>
+      </c>
+      <c r="T323">
+        <v>1.781263545</v>
+      </c>
+      <c r="AD323">
+        <v>-23.19888</v>
+      </c>
+      <c r="AE323">
+        <v>7.06011</v>
+      </c>
+      <c r="AF323">
+        <v>-0.3852589829</v>
+      </c>
+      <c r="AG323">
+        <v>15.24</v>
+      </c>
+      <c r="AH323">
+        <v>1.560905675</v>
+      </c>
+      <c r="AI323">
+        <v>2.008925852</v>
+      </c>
+      <c r="AJ323">
+        <v>-33.04550113</v>
+      </c>
+      <c r="AK323">
+        <v>-1.802907724</v>
+      </c>
+      <c r="AL323">
+        <v>-3.289954071</v>
+      </c>
+      <c r="AM323">
+        <v>6.160254995</v>
+      </c>
+      <c r="AN323">
+        <v>-8.805418769999999</v>
+      </c>
+      <c r="AO323" t="s">
+        <v>755</v>
+      </c>
+      <c r="AP323" t="s">
+        <v>775</v>
+      </c>
+      <c r="AR323" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS323">
+        <v>26100006</v>
+      </c>
+      <c r="AU323">
+        <v>1000542978</v>
+      </c>
+      <c r="AV323" t="s">
+        <v>789</v>
+      </c>
+      <c r="AZ323" t="s">
+        <v>797</v>
+      </c>
+      <c r="BQ323" t="s">
         <v>802</v>
       </c>
-      <c r="BS322" t="s">
-        <v>804</v>
+      <c r="BR323" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS323" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="324" spans="1:71">
+      <c r="A324">
+        <v>157</v>
+      </c>
+      <c r="B324" t="s">
+        <v>74</v>
+      </c>
+      <c r="C324" t="s">
+        <v>383</v>
+      </c>
+      <c r="D324" t="s">
+        <v>400</v>
+      </c>
+      <c r="E324">
+        <v>1000542960</v>
+      </c>
+      <c r="F324" t="s">
+        <v>401</v>
+      </c>
+      <c r="I324" t="s">
+        <v>408</v>
+      </c>
+      <c r="J324" t="s">
+        <v>410</v>
+      </c>
+      <c r="L324">
+        <v>120.12061</v>
+      </c>
+      <c r="M324">
+        <v>-0.7948845742</v>
+      </c>
+      <c r="N324">
+        <v>-1.966797521</v>
+      </c>
+      <c r="O324">
+        <v>1330.405799</v>
+      </c>
+      <c r="P324">
+        <v>233.1834335</v>
+      </c>
+      <c r="Q324" t="s">
+        <v>428</v>
+      </c>
+      <c r="R324">
+        <v>1.621073607</v>
+      </c>
+      <c r="S324">
+        <v>0.5066287591</v>
+      </c>
+      <c r="T324">
+        <v>1.686035136</v>
+      </c>
+      <c r="U324">
+        <v>-101.48252</v>
+      </c>
+      <c r="V324">
+        <v>27.71903</v>
+      </c>
+      <c r="W324">
+        <v>37.16909</v>
+      </c>
+      <c r="X324">
+        <v>0.3796571775</v>
+      </c>
+      <c r="Y324">
+        <v>0.317806977</v>
+      </c>
+      <c r="Z324">
+        <v>110.04409</v>
+      </c>
+      <c r="AA324">
+        <v>-8.22662882</v>
+      </c>
+      <c r="AB324">
+        <v>0.7753054861000001</v>
+      </c>
+      <c r="AC324">
+        <v>0.5133203999</v>
+      </c>
+      <c r="AD324">
+        <v>-21.26566</v>
+      </c>
+      <c r="AE324">
+        <v>15.36266</v>
+      </c>
+      <c r="AF324">
+        <v>-0.4575704663</v>
+      </c>
+      <c r="AG324">
+        <v>15.24</v>
+      </c>
+      <c r="AH324">
+        <v>1.59205043</v>
+      </c>
+      <c r="AI324">
+        <v>1.006990583</v>
+      </c>
+      <c r="AJ324">
+        <v>-33.06921046</v>
+      </c>
+      <c r="AK324">
+        <v>-0.8102656873</v>
+      </c>
+      <c r="AL324">
+        <v>-3.02815701</v>
+      </c>
+      <c r="AM324">
+        <v>6.026416772</v>
+      </c>
+      <c r="AN324">
+        <v>-7.619060518</v>
+      </c>
+      <c r="AO324" t="s">
+        <v>756</v>
+      </c>
+      <c r="AP324" t="s">
+        <v>775</v>
+      </c>
+      <c r="AQ324">
+        <v>118.17181</v>
+      </c>
+      <c r="AR324" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS324">
+        <v>26100006</v>
+      </c>
+      <c r="AU324">
+        <v>1000542959</v>
+      </c>
+      <c r="AV324" t="s">
+        <v>790</v>
+      </c>
+      <c r="AZ324" t="s">
+        <v>797</v>
+      </c>
+      <c r="BQ324" t="s">
+        <v>802</v>
+      </c>
+      <c r="BR324" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS324" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="325" spans="1:71">
+      <c r="A325">
+        <v>148</v>
+      </c>
+      <c r="B325" t="s">
+        <v>74</v>
+      </c>
+      <c r="C325" t="s">
+        <v>384</v>
+      </c>
+      <c r="D325" t="s">
+        <v>400</v>
+      </c>
+      <c r="E325">
+        <v>1000542960</v>
+      </c>
+      <c r="F325" t="s">
+        <v>401</v>
+      </c>
+      <c r="I325" t="s">
+        <v>405</v>
+      </c>
+      <c r="J325" t="s">
+        <v>410</v>
+      </c>
+      <c r="L325">
+        <v>118.30562</v>
+      </c>
+      <c r="M325">
+        <v>1.074070925</v>
+      </c>
+      <c r="N325">
+        <v>-0.9785296691000001</v>
+      </c>
+      <c r="O325">
+        <v>2080.827397</v>
+      </c>
+      <c r="P325">
+        <v>34.73396365</v>
+      </c>
+      <c r="Q325" t="s">
+        <v>439</v>
+      </c>
+      <c r="R325">
+        <v>1.645696215</v>
+      </c>
+      <c r="S325">
+        <v>0.4799919208</v>
+      </c>
+      <c r="T325">
+        <v>1.624554013</v>
+      </c>
+      <c r="U325">
+        <v>-147.01021</v>
+      </c>
+      <c r="V325">
+        <v>-13.14102</v>
+      </c>
+      <c r="W325">
+        <v>-9.03514</v>
+      </c>
+      <c r="X325">
+        <v>0.4828039243</v>
+      </c>
+      <c r="Y325">
+        <v>0.1098041929</v>
+      </c>
+      <c r="Z325">
+        <v>109.07337</v>
+      </c>
+      <c r="AA325">
+        <v>-9.627614417</v>
+      </c>
+      <c r="AB325">
+        <v>-1.641788022</v>
+      </c>
+      <c r="AC325">
+        <v>0.5225104462</v>
+      </c>
+      <c r="AD325">
+        <v>4.07245</v>
+      </c>
+      <c r="AE325">
+        <v>-7.72601</v>
+      </c>
+      <c r="AF325">
+        <v>-0.4523154346</v>
+      </c>
+      <c r="AG325">
+        <v>15.24</v>
+      </c>
+      <c r="AH325">
+        <v>1.662749425</v>
+      </c>
+      <c r="AI325">
+        <v>0.5882842428</v>
+      </c>
+      <c r="AJ325">
+        <v>-32.57625777</v>
+      </c>
+      <c r="AK325">
+        <v>0.09221050119</v>
+      </c>
+      <c r="AL325">
+        <v>0.5640373883000001</v>
+      </c>
+      <c r="AM325">
+        <v>5.728008155</v>
+      </c>
+      <c r="AN325">
+        <v>-10.87670768</v>
+      </c>
+      <c r="AO325" t="s">
+        <v>757</v>
+      </c>
+      <c r="AP325" t="s">
+        <v>775</v>
+      </c>
+      <c r="AQ325">
+        <v>116.09337</v>
+      </c>
+      <c r="AR325" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS325">
+        <v>26100006</v>
+      </c>
+      <c r="AU325">
+        <v>1000542975</v>
+      </c>
+      <c r="AV325" t="s">
+        <v>791</v>
+      </c>
+      <c r="AZ325" t="s">
+        <v>401</v>
+      </c>
+      <c r="BQ325" t="s">
+        <v>802</v>
+      </c>
+      <c r="BR325" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS325" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="326" spans="1:71">
+      <c r="A326">
+        <v>149</v>
+      </c>
+      <c r="B326" t="s">
+        <v>74</v>
+      </c>
+      <c r="C326" t="s">
+        <v>385</v>
+      </c>
+      <c r="D326" t="s">
+        <v>400</v>
+      </c>
+      <c r="E326">
+        <v>1000542960</v>
+      </c>
+      <c r="F326" t="s">
+        <v>401</v>
+      </c>
+      <c r="I326" t="s">
+        <v>405</v>
+      </c>
+      <c r="J326" t="s">
+        <v>410</v>
+      </c>
+      <c r="L326">
+        <v>115.90751</v>
+      </c>
+      <c r="M326">
+        <v>0.3580274847</v>
+      </c>
+      <c r="N326">
+        <v>-2.44978532</v>
+      </c>
+      <c r="O326">
+        <v>2085.874235</v>
+      </c>
+      <c r="P326">
+        <v>19.90145494</v>
+      </c>
+      <c r="Q326" t="s">
+        <v>434</v>
+      </c>
+      <c r="R326">
+        <v>1.650022096</v>
+      </c>
+      <c r="S326">
+        <v>0.468169337</v>
+      </c>
+      <c r="T326">
+        <v>1.686485042</v>
+      </c>
+      <c r="U326">
+        <v>-159.00405</v>
+      </c>
+      <c r="V326">
+        <v>-19.86805</v>
+      </c>
+      <c r="W326">
+        <v>-7.15779</v>
+      </c>
+      <c r="X326">
+        <v>0.1620667167</v>
+      </c>
+      <c r="Y326">
+        <v>-0.3016988045</v>
+      </c>
+      <c r="Z326">
+        <v>106.99998</v>
+      </c>
+      <c r="AA326">
+        <v>-11.22885882</v>
+      </c>
+      <c r="AB326">
+        <v>-2.977475842</v>
+      </c>
+      <c r="AC326">
+        <v>0.5326898307</v>
+      </c>
+      <c r="AD326">
+        <v>1.96254</v>
+      </c>
+      <c r="AE326">
+        <v>-10.86865</v>
+      </c>
+      <c r="AF326">
+        <v>-0.4028535616</v>
+      </c>
+      <c r="AG326">
+        <v>15.24</v>
+      </c>
+      <c r="AH326">
+        <v>1.64697753</v>
+      </c>
+      <c r="AI326">
+        <v>1.388428781</v>
+      </c>
+      <c r="AJ326">
+        <v>-31.89570278</v>
+      </c>
+      <c r="AK326">
+        <v>-0.3300535807</v>
+      </c>
+      <c r="AL326">
+        <v>0.2593312105</v>
+      </c>
+      <c r="AM326">
+        <v>5.730506781</v>
+      </c>
+      <c r="AN326">
+        <v>-11.24284147</v>
+      </c>
+      <c r="AO326" t="s">
+        <v>758</v>
+      </c>
+      <c r="AP326" t="s">
+        <v>775</v>
+      </c>
+      <c r="AQ326">
+        <v>113.8749</v>
+      </c>
+      <c r="AR326" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS326">
+        <v>26100006</v>
+      </c>
+      <c r="AU326">
+        <v>1000542975</v>
+      </c>
+      <c r="AV326" t="s">
+        <v>791</v>
+      </c>
+      <c r="AZ326" t="s">
+        <v>401</v>
+      </c>
+      <c r="BQ326" t="s">
+        <v>802</v>
+      </c>
+      <c r="BR326" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS326" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="327" spans="1:71">
+      <c r="A327">
+        <v>152</v>
+      </c>
+      <c r="B327" t="s">
+        <v>74</v>
+      </c>
+      <c r="C327" t="s">
+        <v>386</v>
+      </c>
+      <c r="D327" t="s">
+        <v>400</v>
+      </c>
+      <c r="E327">
+        <v>1000542960</v>
+      </c>
+      <c r="F327" t="s">
+        <v>401</v>
+      </c>
+      <c r="I327" t="s">
+        <v>405</v>
+      </c>
+      <c r="J327" t="s">
+        <v>410</v>
+      </c>
+      <c r="L327">
+        <v>116.04181</v>
+      </c>
+      <c r="M327">
+        <v>0.6952287346</v>
+      </c>
+      <c r="N327">
+        <v>-1.224605744</v>
+      </c>
+      <c r="O327">
+        <v>1930.502675</v>
+      </c>
+      <c r="P327">
+        <v>107.8113013</v>
+      </c>
+      <c r="Q327" t="s">
+        <v>420</v>
+      </c>
+      <c r="R327">
+        <v>1.64376894</v>
+      </c>
+      <c r="S327">
+        <v>0.4728907649</v>
+      </c>
+      <c r="T327">
+        <v>1.657890975</v>
+      </c>
+      <c r="U327">
+        <v>-132.98594</v>
+      </c>
+      <c r="V327">
+        <v>6.66577</v>
+      </c>
+      <c r="W327">
+        <v>-21.09612</v>
+      </c>
+      <c r="X327">
+        <v>0.5123597399000001</v>
+      </c>
+      <c r="Y327">
+        <v>-0.0875854527</v>
+      </c>
+      <c r="Z327">
+        <v>106.02309</v>
+      </c>
+      <c r="AA327">
+        <v>-9.047368105</v>
+      </c>
+      <c r="AB327">
+        <v>-2.781900869</v>
+      </c>
+      <c r="AC327">
+        <v>0.5336761434</v>
+      </c>
+      <c r="AD327">
+        <v>10.26288</v>
+      </c>
+      <c r="AE327">
+        <v>3.00017</v>
+      </c>
+      <c r="AF327">
+        <v>-0.4382141122</v>
+      </c>
+      <c r="AG327">
+        <v>15.24</v>
+      </c>
+      <c r="AH327">
+        <v>1.651697156</v>
+      </c>
+      <c r="AI327">
+        <v>0.7539426138999999</v>
+      </c>
+      <c r="AJ327">
+        <v>-31.93822045</v>
+      </c>
+      <c r="AK327">
+        <v>-0.06124869329</v>
+      </c>
+      <c r="AL327">
+        <v>1.354283126</v>
+      </c>
+      <c r="AM327">
+        <v>5.947287104</v>
+      </c>
+      <c r="AN327">
+        <v>-9.410749704000001</v>
+      </c>
+      <c r="AO327" t="s">
+        <v>759</v>
+      </c>
+      <c r="AP327" t="s">
+        <v>775</v>
+      </c>
+      <c r="AQ327">
+        <v>113.66444</v>
+      </c>
+      <c r="AR327" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS327">
+        <v>26100006</v>
+      </c>
+      <c r="AU327">
+        <v>1000542978</v>
+      </c>
+      <c r="AV327" t="s">
+        <v>789</v>
+      </c>
+      <c r="AZ327" t="s">
+        <v>797</v>
+      </c>
+      <c r="BQ327" t="s">
+        <v>802</v>
+      </c>
+      <c r="BR327" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS327" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="328" spans="1:71">
+      <c r="A328">
+        <v>146</v>
+      </c>
+      <c r="B328" t="s">
+        <v>74</v>
+      </c>
+      <c r="C328" t="s">
+        <v>387</v>
+      </c>
+      <c r="D328" t="s">
+        <v>400</v>
+      </c>
+      <c r="E328">
+        <v>1000542960</v>
+      </c>
+      <c r="F328" t="s">
+        <v>401</v>
+      </c>
+      <c r="I328" t="s">
+        <v>402</v>
+      </c>
+      <c r="J328" t="s">
+        <v>410</v>
+      </c>
+      <c r="L328">
+        <v>135.60126</v>
+      </c>
+      <c r="M328">
+        <v>0.4787425399</v>
+      </c>
+      <c r="N328">
+        <v>-1.754996706</v>
+      </c>
+      <c r="O328">
+        <v>1848.282116</v>
+      </c>
+      <c r="P328">
+        <v>201.1606933</v>
+      </c>
+      <c r="Q328" t="s">
+        <v>413</v>
+      </c>
+      <c r="R328">
+        <v>1.65099071</v>
+      </c>
+      <c r="S328">
+        <v>0.5263070573</v>
+      </c>
+      <c r="T328">
+        <v>1.75895723</v>
+      </c>
+      <c r="U328">
+        <v>-53.24809</v>
+      </c>
+      <c r="V328">
+        <v>46.54082</v>
+      </c>
+      <c r="W328">
+        <v>18.05712</v>
+      </c>
+      <c r="X328">
+        <v>1.254349448</v>
+      </c>
+      <c r="Y328">
+        <v>0.2090005537</v>
+      </c>
+      <c r="Z328">
+        <v>124.03537</v>
+      </c>
+      <c r="AA328">
+        <v>-3.449692342</v>
+      </c>
+      <c r="AB328">
+        <v>-0.4218275353</v>
+      </c>
+      <c r="AC328">
+        <v>0.4511238642</v>
+      </c>
+      <c r="AD328">
+        <v>-10.89933</v>
+      </c>
+      <c r="AE328">
+        <v>24.64866</v>
+      </c>
+      <c r="AF328">
+        <v>-0.4834630053</v>
+      </c>
+      <c r="AG328">
+        <v>15.24</v>
+      </c>
+      <c r="AH328">
+        <v>1.65917569</v>
+      </c>
+      <c r="AI328">
+        <v>1.07686397</v>
+      </c>
+      <c r="AJ328">
+        <v>-37.37065321</v>
+      </c>
+      <c r="AK328">
+        <v>0.1113705209</v>
+      </c>
+      <c r="AL328">
+        <v>-1.995766161</v>
+      </c>
+      <c r="AM328">
+        <v>7.220026269</v>
+      </c>
+      <c r="AN328">
+        <v>-5.293257119</v>
+      </c>
+      <c r="AO328" t="s">
+        <v>760</v>
+      </c>
+      <c r="AP328" t="s">
+        <v>774</v>
+      </c>
+      <c r="AQ328">
+        <v>134.46418</v>
+      </c>
+      <c r="AR328" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS328">
+        <v>26100006</v>
+      </c>
+      <c r="AU328">
+        <v>1000542949</v>
+      </c>
+      <c r="AV328" t="s">
+        <v>792</v>
+      </c>
+      <c r="AX328" t="s">
+        <v>796</v>
+      </c>
+      <c r="AZ328" t="s">
+        <v>797</v>
+      </c>
+      <c r="BQ328" t="s">
+        <v>802</v>
+      </c>
+      <c r="BR328" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS328" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="329" spans="1:71">
+      <c r="A329">
+        <v>147</v>
+      </c>
+      <c r="B329" t="s">
+        <v>74</v>
+      </c>
+      <c r="C329" t="s">
+        <v>388</v>
+      </c>
+      <c r="D329" t="s">
+        <v>400</v>
+      </c>
+      <c r="E329">
+        <v>1000542960</v>
+      </c>
+      <c r="F329" t="s">
+        <v>401</v>
+      </c>
+      <c r="I329" t="s">
+        <v>402</v>
+      </c>
+      <c r="J329" t="s">
+        <v>410</v>
+      </c>
+      <c r="L329">
+        <v>135.57907</v>
+      </c>
+      <c r="M329">
+        <v>-1.777233632</v>
+      </c>
+      <c r="N329">
+        <v>-2.841791361</v>
+      </c>
+      <c r="O329">
+        <v>1943.778092</v>
+      </c>
+      <c r="P329">
+        <v>205.4011146</v>
+      </c>
+      <c r="Q329" t="s">
+        <v>413</v>
+      </c>
+      <c r="R329">
+        <v>1.67194725</v>
+      </c>
+      <c r="S329">
+        <v>0.5324969708</v>
+      </c>
+      <c r="T329">
+        <v>1.766260715</v>
+      </c>
+      <c r="U329">
+        <v>-52.88832</v>
+      </c>
+      <c r="V329">
+        <v>45.68454</v>
+      </c>
+      <c r="W329">
+        <v>21.73315</v>
+      </c>
+      <c r="X329">
+        <v>0.6384799878</v>
+      </c>
+      <c r="Y329">
+        <v>-0.05641052044</v>
+      </c>
+      <c r="Z329">
+        <v>126.11057</v>
+      </c>
+      <c r="AA329">
+        <v>-5.638658778</v>
+      </c>
+      <c r="AB329">
+        <v>-1.250239361</v>
+      </c>
+      <c r="AC329">
+        <v>0.448366695</v>
+      </c>
+      <c r="AD329">
+        <v>-13.26297</v>
+      </c>
+      <c r="AE329">
+        <v>25.46798</v>
+      </c>
+      <c r="AF329">
+        <v>-0.4629091288</v>
+      </c>
+      <c r="AG329">
+        <v>15.24</v>
+      </c>
+      <c r="AH329">
+        <v>1.62355576</v>
+      </c>
+      <c r="AI329">
+        <v>1.771931889</v>
+      </c>
+      <c r="AJ329">
+        <v>-37.36237002</v>
+      </c>
+      <c r="AK329">
+        <v>-1.362006842</v>
+      </c>
+      <c r="AL329">
+        <v>-2.465890752</v>
+      </c>
+      <c r="AM329">
+        <v>6.118947232</v>
+      </c>
+      <c r="AN329">
+        <v>-5.071568202</v>
+      </c>
+      <c r="AO329" t="s">
+        <v>761</v>
+      </c>
+      <c r="AP329" t="s">
+        <v>774</v>
+      </c>
+      <c r="AQ329">
+        <v>135.29105</v>
+      </c>
+      <c r="AR329" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS329">
+        <v>26100006</v>
+      </c>
+      <c r="AU329">
+        <v>1000542975</v>
+      </c>
+      <c r="AV329" t="s">
+        <v>791</v>
+      </c>
+      <c r="AZ329" t="s">
+        <v>401</v>
+      </c>
+      <c r="BQ329" t="s">
+        <v>802</v>
+      </c>
+      <c r="BR329" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS329" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="330" spans="1:71">
+      <c r="A330">
+        <v>150</v>
+      </c>
+      <c r="B330" t="s">
+        <v>74</v>
+      </c>
+      <c r="C330" t="s">
+        <v>389</v>
+      </c>
+      <c r="D330" t="s">
+        <v>400</v>
+      </c>
+      <c r="E330">
+        <v>1000542960</v>
+      </c>
+      <c r="F330" t="s">
+        <v>401</v>
+      </c>
+      <c r="I330" t="s">
+        <v>402</v>
+      </c>
+      <c r="J330" t="s">
+        <v>410</v>
+      </c>
+      <c r="L330">
+        <v>132.95849</v>
+      </c>
+      <c r="M330">
+        <v>-1.397371956</v>
+      </c>
+      <c r="N330">
+        <v>-1.343184271</v>
+      </c>
+      <c r="O330">
+        <v>1692.843504</v>
+      </c>
+      <c r="P330">
+        <v>219.6212185</v>
+      </c>
+      <c r="Q330" t="s">
+        <v>414</v>
+      </c>
+      <c r="R330">
+        <v>1.641156233</v>
+      </c>
+      <c r="S330">
+        <v>0.5363284399</v>
+      </c>
+      <c r="T330">
+        <v>1.776763448</v>
+      </c>
+      <c r="U330">
+        <v>-74.25409000000001</v>
+      </c>
+      <c r="V330">
+        <v>29.5255</v>
+      </c>
+      <c r="W330">
+        <v>24.50354</v>
+      </c>
+      <c r="X330">
+        <v>0.5025636482</v>
+      </c>
+      <c r="Y330">
+        <v>0.4007807784</v>
+      </c>
+      <c r="Z330">
+        <v>122.02186</v>
+      </c>
+      <c r="AA330">
+        <v>-6.861024701</v>
+      </c>
+      <c r="AB330">
+        <v>0.470284851</v>
+      </c>
+      <c r="AC330">
+        <v>0.460055945</v>
+      </c>
+      <c r="AD330">
+        <v>-14.13211</v>
+      </c>
+      <c r="AE330">
+        <v>16.87297</v>
+      </c>
+      <c r="AF330">
+        <v>-0.5046914591</v>
+      </c>
+      <c r="AG330">
+        <v>15.24</v>
+      </c>
+      <c r="AH330">
+        <v>1.601174034</v>
+      </c>
+      <c r="AI330">
+        <v>0.7694373815</v>
+      </c>
+      <c r="AJ330">
+        <v>-36.63748341</v>
+      </c>
+      <c r="AK330">
+        <v>-1.165520096</v>
+      </c>
+      <c r="AL330">
+        <v>-2.481646318</v>
+      </c>
+      <c r="AM330">
+        <v>7.087581588</v>
+      </c>
+      <c r="AN330">
+        <v>-6.843699429</v>
+      </c>
+      <c r="AO330" t="s">
+        <v>762</v>
+      </c>
+      <c r="AP330" t="s">
+        <v>775</v>
+      </c>
+      <c r="AQ330">
+        <v>131.85353</v>
+      </c>
+      <c r="AR330" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS330">
+        <v>26100006</v>
+      </c>
+      <c r="AU330">
+        <v>1000542978</v>
+      </c>
+      <c r="AV330" t="s">
+        <v>789</v>
+      </c>
+      <c r="AZ330" t="s">
+        <v>797</v>
+      </c>
+      <c r="BQ330" t="s">
+        <v>802</v>
+      </c>
+      <c r="BR330" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS330" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="331" spans="1:71">
+      <c r="A331">
+        <v>151</v>
+      </c>
+      <c r="B331" t="s">
+        <v>74</v>
+      </c>
+      <c r="C331" t="s">
+        <v>390</v>
+      </c>
+      <c r="D331" t="s">
+        <v>400</v>
+      </c>
+      <c r="E331">
+        <v>1000542960</v>
+      </c>
+      <c r="F331" t="s">
+        <v>401</v>
+      </c>
+      <c r="I331" t="s">
+        <v>402</v>
+      </c>
+      <c r="J331" t="s">
+        <v>410</v>
+      </c>
+      <c r="L331">
+        <v>132.0481</v>
+      </c>
+      <c r="M331">
+        <v>0.9383774608</v>
+      </c>
+      <c r="N331">
+        <v>-1.730677332</v>
+      </c>
+      <c r="O331">
+        <v>1662.019565</v>
+      </c>
+      <c r="P331">
+        <v>203.6458455</v>
+      </c>
+      <c r="Q331" t="s">
+        <v>413</v>
+      </c>
+      <c r="R331">
+        <v>1.630309255</v>
+      </c>
+      <c r="S331">
+        <v>0.5395545533</v>
+      </c>
+      <c r="T331">
+        <v>1.833558689</v>
+      </c>
+      <c r="U331">
+        <v>-61.19528</v>
+      </c>
+      <c r="V331">
+        <v>44.29423</v>
+      </c>
+      <c r="W331">
+        <v>19.44289</v>
+      </c>
+      <c r="X331">
+        <v>1.28340567</v>
+      </c>
+      <c r="Y331">
+        <v>0.2452632823</v>
+      </c>
+      <c r="Z331">
+        <v>119.34768</v>
+      </c>
+      <c r="AA331">
+        <v>-3.625787355</v>
+      </c>
+      <c r="AB331">
+        <v>-0.2793642515</v>
+      </c>
+      <c r="AC331">
+        <v>0.4638305066</v>
+      </c>
+      <c r="AD331">
+        <v>-11.92093</v>
+      </c>
+      <c r="AE331">
+        <v>23.3221</v>
+      </c>
+      <c r="AF331">
+        <v>-0.4995328356</v>
+      </c>
+      <c r="AG331">
+        <v>15.24</v>
+      </c>
+      <c r="AH331">
+        <v>1.648717322</v>
+      </c>
+      <c r="AI331">
+        <v>1.031290749</v>
+      </c>
+      <c r="AJ331">
+        <v>-36.37010753</v>
+      </c>
+      <c r="AK331">
+        <v>0.3830951691</v>
+      </c>
+      <c r="AL331">
+        <v>-2.040229561</v>
+      </c>
+      <c r="AM331">
+        <v>7.703240782</v>
+      </c>
+      <c r="AN331">
+        <v>-5.815144406</v>
+      </c>
+      <c r="AO331" t="s">
+        <v>763</v>
+      </c>
+      <c r="AP331" t="s">
+        <v>775</v>
+      </c>
+      <c r="AQ331">
+        <v>130.78053</v>
+      </c>
+      <c r="AR331" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS331">
+        <v>26100006</v>
+      </c>
+      <c r="AU331">
+        <v>1000542978</v>
+      </c>
+      <c r="AV331" t="s">
+        <v>789</v>
+      </c>
+      <c r="AZ331" t="s">
+        <v>797</v>
+      </c>
+      <c r="BQ331" t="s">
+        <v>802</v>
+      </c>
+      <c r="BR331" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS331" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="332" spans="1:71">
+      <c r="A332">
+        <v>154</v>
+      </c>
+      <c r="B332" t="s">
+        <v>74</v>
+      </c>
+      <c r="C332" t="s">
+        <v>391</v>
+      </c>
+      <c r="D332" t="s">
+        <v>400</v>
+      </c>
+      <c r="E332">
+        <v>1000542960</v>
+      </c>
+      <c r="F332" t="s">
+        <v>401</v>
+      </c>
+      <c r="I332" t="s">
+        <v>402</v>
+      </c>
+      <c r="J332" t="s">
+        <v>410</v>
+      </c>
+      <c r="L332">
+        <v>134.04265</v>
+      </c>
+      <c r="M332">
+        <v>-0.09038173556</v>
+      </c>
+      <c r="N332">
+        <v>-1.248446607</v>
+      </c>
+      <c r="O332">
+        <v>1821.091007</v>
+      </c>
+      <c r="P332">
+        <v>207.3871378</v>
+      </c>
+      <c r="Q332" t="s">
+        <v>411</v>
+      </c>
+      <c r="R332">
+        <v>1.633730798</v>
+      </c>
+      <c r="S332">
+        <v>0.5066866632</v>
+      </c>
+      <c r="T332">
+        <v>1.798154606</v>
+      </c>
+      <c r="U332">
+        <v>-60.17722</v>
+      </c>
+      <c r="V332">
+        <v>42.26408</v>
+      </c>
+      <c r="W332">
+        <v>21.94464</v>
+      </c>
+      <c r="X332">
+        <v>1.006381832</v>
+      </c>
+      <c r="Y332">
+        <v>0.37286825</v>
+      </c>
+      <c r="Z332">
+        <v>121.72018</v>
+      </c>
+      <c r="AA332">
+        <v>-4.556948019</v>
+      </c>
+      <c r="AB332">
+        <v>0.3837008783</v>
+      </c>
+      <c r="AC332">
+        <v>0.4570799822</v>
+      </c>
+      <c r="AD332">
+        <v>-12.808</v>
+      </c>
+      <c r="AE332">
+        <v>22.91041</v>
+      </c>
+      <c r="AF332">
+        <v>-0.4776376275</v>
+      </c>
+      <c r="AG332">
+        <v>15.24</v>
+      </c>
+      <c r="AH332">
+        <v>1.627401928</v>
+      </c>
+      <c r="AI332">
+        <v>0.7254768403</v>
+      </c>
+      <c r="AJ332">
+        <v>-36.9338971</v>
+      </c>
+      <c r="AK332">
+        <v>-0.2760684679</v>
+      </c>
+      <c r="AL332">
+        <v>-2.268656088</v>
+      </c>
+      <c r="AM332">
+        <v>7.704694641</v>
+      </c>
+      <c r="AN332">
+        <v>-5.748575746</v>
+      </c>
+      <c r="AO332" t="s">
+        <v>764</v>
+      </c>
+      <c r="AP332" t="s">
+        <v>775</v>
+      </c>
+      <c r="AQ332">
+        <v>132.712</v>
+      </c>
+      <c r="AR332" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS332">
+        <v>26100006</v>
+      </c>
+      <c r="AU332">
+        <v>1000542978</v>
+      </c>
+      <c r="AV332" t="s">
+        <v>789</v>
+      </c>
+      <c r="AZ332" t="s">
+        <v>797</v>
+      </c>
+      <c r="BQ332" t="s">
+        <v>802</v>
+      </c>
+      <c r="BR332" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS332" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="333" spans="1:71">
+      <c r="A333">
+        <v>155</v>
+      </c>
+      <c r="B333" t="s">
+        <v>74</v>
+      </c>
+      <c r="C333" t="s">
+        <v>392</v>
+      </c>
+      <c r="D333" t="s">
+        <v>400</v>
+      </c>
+      <c r="E333">
+        <v>1000542960</v>
+      </c>
+      <c r="F333" t="s">
+        <v>401</v>
+      </c>
+      <c r="I333" t="s">
+        <v>402</v>
+      </c>
+      <c r="J333" t="s">
+        <v>410</v>
+      </c>
+      <c r="L333">
+        <v>131.77579</v>
+      </c>
+      <c r="M333">
+        <v>-1.470812964</v>
+      </c>
+      <c r="N333">
+        <v>-2.480548599</v>
+      </c>
+      <c r="O333">
+        <v>1835.701652</v>
+      </c>
+      <c r="P333">
+        <v>206.773211</v>
+      </c>
+      <c r="Q333" t="s">
+        <v>411</v>
+      </c>
+      <c r="R333">
+        <v>1.629009553</v>
+      </c>
+      <c r="S333">
+        <v>0.4965447441</v>
+      </c>
+      <c r="T333">
+        <v>1.785602981</v>
+      </c>
+      <c r="U333">
+        <v>-60.48254</v>
+      </c>
+      <c r="V333">
+        <v>46.86769</v>
+      </c>
+      <c r="W333">
+        <v>23.69336</v>
+      </c>
+      <c r="X333">
+        <v>0.6072593031</v>
+      </c>
+      <c r="Y333">
+        <v>0.03070232015</v>
+      </c>
+      <c r="Z333">
+        <v>118.67348</v>
+      </c>
+      <c r="AA333">
+        <v>-5.968611823</v>
+      </c>
+      <c r="AB333">
+        <v>-0.7120914532</v>
+      </c>
+      <c r="AC333">
+        <v>0.4679033556</v>
+      </c>
+      <c r="AD333">
+        <v>-14.88718</v>
+      </c>
+      <c r="AE333">
+        <v>26.58237</v>
+      </c>
+      <c r="AF333">
+        <v>-0.4369057832</v>
+      </c>
+      <c r="AG333">
+        <v>15.24</v>
+      </c>
+      <c r="AH333">
+        <v>1.588488309</v>
+      </c>
+      <c r="AI333">
+        <v>1.486044963</v>
+      </c>
+      <c r="AJ333">
+        <v>-36.24460201</v>
+      </c>
+      <c r="AK333">
+        <v>-1.146180573</v>
+      </c>
+      <c r="AL333">
+        <v>-2.513888311</v>
+      </c>
+      <c r="AM333">
+        <v>8.066654379999999</v>
+      </c>
+      <c r="AN333">
+        <v>-5.317881231</v>
+      </c>
+      <c r="AO333" t="s">
+        <v>765</v>
+      </c>
+      <c r="AP333" t="s">
+        <v>775</v>
+      </c>
+      <c r="AQ333">
+        <v>129.64216</v>
+      </c>
+      <c r="AR333" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS333">
+        <v>26100006</v>
+      </c>
+      <c r="AU333">
+        <v>1000542957</v>
+      </c>
+      <c r="AV333" t="s">
+        <v>788</v>
+      </c>
+      <c r="AX333" t="s">
+        <v>796</v>
+      </c>
+      <c r="AZ333" t="s">
+        <v>797</v>
+      </c>
+      <c r="BQ333" t="s">
+        <v>802</v>
+      </c>
+      <c r="BR333" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS333" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="334" spans="1:71">
+      <c r="A334">
+        <v>156</v>
+      </c>
+      <c r="B334" t="s">
+        <v>74</v>
+      </c>
+      <c r="C334" t="s">
+        <v>393</v>
+      </c>
+      <c r="D334" t="s">
+        <v>400</v>
+      </c>
+      <c r="E334">
+        <v>1000542960</v>
+      </c>
+      <c r="F334" t="s">
+        <v>401</v>
+      </c>
+      <c r="I334" t="s">
+        <v>402</v>
+      </c>
+      <c r="J334" t="s">
+        <v>410</v>
+      </c>
+      <c r="L334">
+        <v>133.06821</v>
+      </c>
+      <c r="M334">
+        <v>-1.492781842</v>
+      </c>
+      <c r="N334">
+        <v>-1.616473505</v>
+      </c>
+      <c r="O334">
+        <v>1899.929566</v>
+      </c>
+      <c r="P334">
+        <v>206.2391731</v>
+      </c>
+      <c r="Q334" t="s">
+        <v>413</v>
+      </c>
+      <c r="R334">
+        <v>1.62603186</v>
+      </c>
+      <c r="S334">
+        <v>0.5384297353</v>
+      </c>
+      <c r="T334">
+        <v>1.74064373</v>
+      </c>
+      <c r="U334">
+        <v>-62.47635</v>
+      </c>
+      <c r="V334">
+        <v>42.42285</v>
+      </c>
+      <c r="W334">
+        <v>20.94743</v>
+      </c>
+      <c r="X334">
+        <v>0.5771694248</v>
+      </c>
+      <c r="Y334">
+        <v>0.2888291356</v>
+      </c>
+      <c r="Z334">
+        <v>120.94504</v>
+      </c>
+      <c r="AA334">
+        <v>-6.104036397</v>
+      </c>
+      <c r="AB334">
+        <v>-0.06334774945</v>
+      </c>
+      <c r="AC334">
+        <v>0.4625308962</v>
+      </c>
+      <c r="AD334">
+        <v>-12.48449</v>
+      </c>
+      <c r="AE334">
+        <v>23.92097</v>
+      </c>
+      <c r="AF334">
+        <v>-0.4987874084</v>
+      </c>
+      <c r="AG334">
+        <v>15.24</v>
+      </c>
+      <c r="AH334">
+        <v>1.583389642</v>
+      </c>
+      <c r="AI334">
+        <v>0.956110047</v>
+      </c>
+      <c r="AJ334">
+        <v>-36.63329289</v>
+      </c>
+      <c r="AK334">
+        <v>-1.186755546</v>
+      </c>
+      <c r="AL334">
+        <v>-2.173723138</v>
+      </c>
+      <c r="AM334">
+        <v>7.633629065</v>
+      </c>
+      <c r="AN334">
+        <v>-5.641679331</v>
+      </c>
+      <c r="AO334" t="s">
+        <v>766</v>
+      </c>
+      <c r="AP334" t="s">
+        <v>775</v>
+      </c>
+      <c r="AQ334">
+        <v>131.148</v>
+      </c>
+      <c r="AR334" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS334">
+        <v>26100006</v>
+      </c>
+      <c r="AU334">
+        <v>1000542959</v>
+      </c>
+      <c r="AV334" t="s">
+        <v>790</v>
+      </c>
+      <c r="AZ334" t="s">
+        <v>797</v>
+      </c>
+      <c r="BQ334" t="s">
+        <v>802</v>
+      </c>
+      <c r="BR334" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS334" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="335" spans="1:71">
+      <c r="A335">
+        <v>158</v>
+      </c>
+      <c r="B335" t="s">
+        <v>74</v>
+      </c>
+      <c r="C335" t="s">
+        <v>394</v>
+      </c>
+      <c r="D335" t="s">
+        <v>400</v>
+      </c>
+      <c r="E335">
+        <v>1000542960</v>
+      </c>
+      <c r="F335" t="s">
+        <v>401</v>
+      </c>
+      <c r="I335" t="s">
+        <v>402</v>
+      </c>
+      <c r="J335" t="s">
+        <v>410</v>
+      </c>
+      <c r="L335">
+        <v>133.19387</v>
+      </c>
+      <c r="M335">
+        <v>-1.81226406</v>
+      </c>
+      <c r="N335">
+        <v>-3.546852617</v>
+      </c>
+      <c r="O335">
+        <v>1878.419356</v>
+      </c>
+      <c r="P335">
+        <v>204.0130494</v>
+      </c>
+      <c r="Q335" t="s">
+        <v>413</v>
+      </c>
+      <c r="R335">
+        <v>1.625050034</v>
+      </c>
+      <c r="S335">
+        <v>0.535015536</v>
+      </c>
+      <c r="T335">
+        <v>1.847913509</v>
+      </c>
+      <c r="U335">
+        <v>-54.74202</v>
+      </c>
+      <c r="V335">
+        <v>49.22226</v>
+      </c>
+      <c r="W335">
+        <v>21.97918</v>
+      </c>
+      <c r="X335">
+        <v>0.5653285166000001</v>
+      </c>
+      <c r="Y335">
+        <v>-0.2468630758</v>
+      </c>
+      <c r="Z335">
+        <v>120.51756</v>
+      </c>
+      <c r="AA335">
+        <v>-5.885503362</v>
+      </c>
+      <c r="AB335">
+        <v>-1.907239377</v>
+      </c>
+      <c r="AC335">
+        <v>0.460465118</v>
+      </c>
+      <c r="AD335">
+        <v>-14.77847</v>
+      </c>
+      <c r="AE335">
+        <v>28.22886</v>
+      </c>
+      <c r="AF335">
+        <v>-0.4526106062</v>
+      </c>
+      <c r="AG335">
+        <v>15.24</v>
+      </c>
+      <c r="AH335">
+        <v>1.578695069</v>
+      </c>
+      <c r="AI335">
+        <v>2.193541859</v>
+      </c>
+      <c r="AJ335">
+        <v>-36.61928716</v>
+      </c>
+      <c r="AK335">
+        <v>-1.350782789</v>
+      </c>
+      <c r="AL335">
+        <v>-2.561433578</v>
+      </c>
+      <c r="AM335">
+        <v>7.876315371</v>
+      </c>
+      <c r="AN335">
+        <v>-4.913967651</v>
+      </c>
+      <c r="AO335" t="s">
+        <v>767</v>
+      </c>
+      <c r="AP335" t="s">
+        <v>775</v>
+      </c>
+      <c r="AQ335">
+        <v>131.73636</v>
+      </c>
+      <c r="AR335" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS335">
+        <v>26100006</v>
+      </c>
+      <c r="AT335">
+        <v>-7.512153615</v>
+      </c>
+      <c r="AU335">
+        <v>1000542959</v>
+      </c>
+      <c r="AV335" t="s">
+        <v>790</v>
+      </c>
+      <c r="AX335" t="s">
+        <v>794</v>
+      </c>
+      <c r="AY335">
+        <v>133.9984</v>
+      </c>
+      <c r="AZ335" t="s">
+        <v>797</v>
+      </c>
+      <c r="BA335">
+        <v>28.2710302</v>
+      </c>
+      <c r="BE335">
+        <v>89.18936085999999</v>
+      </c>
+      <c r="BF335">
+        <v>24.25413711</v>
+      </c>
+      <c r="BG335">
+        <v>3.720465432</v>
+      </c>
+      <c r="BH335">
+        <v>-12.33281733</v>
+      </c>
+      <c r="BI335">
+        <v>0.2514615859</v>
+      </c>
+      <c r="BJ335">
+        <v>0.5930941189</v>
+      </c>
+      <c r="BK335">
+        <v>0.2778151873</v>
+      </c>
+      <c r="BQ335" t="s">
+        <v>802</v>
+      </c>
+      <c r="BR335" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS335" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="336" spans="1:71">
+      <c r="A336">
+        <v>145</v>
+      </c>
+      <c r="B336" t="s">
+        <v>74</v>
+      </c>
+      <c r="C336" t="s">
+        <v>395</v>
+      </c>
+      <c r="D336" t="s">
+        <v>400</v>
+      </c>
+      <c r="E336">
+        <v>1000542960</v>
+      </c>
+      <c r="F336" t="s">
+        <v>401</v>
+      </c>
+      <c r="I336" t="s">
+        <v>405</v>
+      </c>
+      <c r="J336" t="s">
+        <v>410</v>
+      </c>
+      <c r="L336">
+        <v>114.11853</v>
+      </c>
+      <c r="M336">
+        <v>2.539292075</v>
+      </c>
+      <c r="N336">
+        <v>-1.340765114</v>
+      </c>
+      <c r="O336">
+        <v>2045.43137</v>
+      </c>
+      <c r="P336">
+        <v>75.62202838</v>
+      </c>
+      <c r="Q336" t="s">
+        <v>446</v>
+      </c>
+      <c r="R336">
+        <v>1.658984152</v>
+      </c>
+      <c r="S336">
+        <v>0.5201749668</v>
+      </c>
+      <c r="T336">
+        <v>1.705596364</v>
+      </c>
+      <c r="U336">
+        <v>-155.38395</v>
+      </c>
+      <c r="V336">
+        <v>-10.93178</v>
+      </c>
+      <c r="W336">
+        <v>-42.31587</v>
+      </c>
+      <c r="X336">
+        <v>0.8283312861</v>
+      </c>
+      <c r="Y336">
+        <v>-0.2845468204</v>
+      </c>
+      <c r="Z336">
+        <v>103.84765</v>
+      </c>
+      <c r="AA336">
+        <v>-8.904736365</v>
+      </c>
+      <c r="AB336">
+        <v>-4.476282788</v>
+      </c>
+      <c r="AC336">
+        <v>0.5427710736</v>
+      </c>
+      <c r="AD336">
+        <v>21.56709</v>
+      </c>
+      <c r="AE336">
+        <v>-7.95206</v>
+      </c>
+      <c r="AF336">
+        <v>-0.4819692252</v>
+      </c>
+      <c r="AG336">
+        <v>15.24</v>
+      </c>
+      <c r="AH336">
+        <v>1.713418687</v>
+      </c>
+      <c r="AI336">
+        <v>0.8705685778</v>
+      </c>
+      <c r="AJ336">
+        <v>-31.37607499</v>
+      </c>
+      <c r="AK336">
+        <v>0.8916841043</v>
+      </c>
+      <c r="AL336">
+        <v>2.732712432</v>
+      </c>
+      <c r="AM336">
+        <v>5.983809762</v>
+      </c>
+      <c r="AN336">
+        <v>-10.8142358</v>
+      </c>
+      <c r="AO336" t="s">
+        <v>768</v>
+      </c>
+      <c r="AP336" t="s">
+        <v>774</v>
+      </c>
+      <c r="AQ336">
+        <v>111.75982</v>
+      </c>
+      <c r="AR336" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS336">
+        <v>26100006</v>
+      </c>
+      <c r="AU336">
+        <v>1000542949</v>
+      </c>
+      <c r="AV336" t="s">
+        <v>792</v>
+      </c>
+      <c r="AZ336" t="s">
+        <v>797</v>
+      </c>
+      <c r="BQ336" t="s">
+        <v>802</v>
+      </c>
+      <c r="BR336" t="s">
+        <v>803</v>
+      </c>
+      <c r="BS336" t="s">
+        <v>805</v>
       </c>
     </row>
   </sheetData>
